--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.8.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="49" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.8.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.8.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0008.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0008.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -609,16 +609,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: practitioners, and to those who have not hitherto been much in this Courtâ€”â€”</t>
+          <t>L21: stray/suspicious non-ASCII glyph(s): U+5C0F CJK UNIFIED IDEOGRAPH-5C0F, U+4E0D CJK UNIFIED IDEOGRAPH-4E0D :: 小 不</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L10: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: To other members of the Profession,â€”to the country practi-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]INTRODUCTORY REMARKS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: ,</t>
@@ -636,7 +640,11 @@
       </c>
       <c r="Q2" s="1" t="inlineStr"/>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tioners, and to those who have not hitherto been much in this Court—</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -657,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,12 +680,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prior to March, 1837, the date of our first Chancery Act â€” among the</t>
+          <t>L32: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: others according to their subject matter ； but, as they have not</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ tioners, and to those who have not hitherto been much in this Courtâ€”</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • tioners, and to those who have not hitherto been much in this Court—</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -721,16 +729,8 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00B8 CEDILLA :: å°� ä¸�</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L17: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: prior to March, 1837, the date of our first Chancery Actâ€”among the</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
